--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,6 +900,628 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129675765</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52250), Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>711606</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6365241</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gran, död.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129675592</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52250), Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>711593</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6365259</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkyta.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129675619</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52250), Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>711485</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6365162</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Svamp i backtimjan; bilder.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkgrus.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129675766</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52250), Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>711600</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6365214</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tall, död.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129675767</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52250), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>711600</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6365189</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gran, död.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129675591</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Altajme 1:35 (A 52250), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>711599</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6365265</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog på kalkyta.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>86996</v>
+        <v>87002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129675765</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107085</v>
+        <v>107097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107085</v>
+        <v>107097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129675766</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>129675767</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107085</v>
+        <v>107097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87002</v>
+        <v>87003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129675765</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107097</v>
+        <v>107098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107097</v>
+        <v>107098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129675766</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>129675767</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107097</v>
+        <v>107098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87003</v>
+        <v>87008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107098</v>
+        <v>107103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107098</v>
+        <v>107103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107098</v>
+        <v>107103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87008</v>
+        <v>87012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87012</v>
+        <v>87014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107107</v>
+        <v>107109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107107</v>
+        <v>107109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107107</v>
+        <v>107109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107109</v>
+        <v>107119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107109</v>
+        <v>107119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107109</v>
+        <v>107119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87014</v>
+        <v>87017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129675765</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107119</v>
+        <v>107123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107119</v>
+        <v>107123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129675766</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>129675767</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107119</v>
+        <v>107123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129675765</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107123</v>
+        <v>107126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107123</v>
+        <v>107126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129675766</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>129675767</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107123</v>
+        <v>107126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129670378</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129670412</v>
       </c>
       <c r="B3" t="n">
-        <v>87020</v>
+        <v>87021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52250-2025 artfynd.xlsx
+++ b/artfynd/A 52250-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>129675592</v>
       </c>
       <c r="B5" t="n">
-        <v>107127</v>
+        <v>107144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>129675619</v>
       </c>
       <c r="B6" t="n">
-        <v>107127</v>
+        <v>107144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>129675591</v>
       </c>
       <c r="B9" t="n">
-        <v>107127</v>
+        <v>107144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
